--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_11_Full_122_Cau/Day_11_Ngan_Hang_Phan_05_20_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_11_Full_122_Cau/Day_11_Ngan_Hang_Phan_05_20_Cau.xlsx
@@ -921,7 +921,7 @@
       <c r="J10" s="3" t="n"/>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Bằng chứng nào độc lập với lời agent tự khai?</t>
+          <t>Lời tự khai của agent không thể coi là bằng chứng xác thực an toàn; oracle kiểm thử bắt buộc phải quan sát các sink thực tế (canary tokens, lệnh gọi công cụ, lưu lượng mạng và thay đổi trạng thái bên ngoài).</t>
         </is>
       </c>
     </row>
@@ -1007,7 +1007,7 @@
       <c r="J12" s="3" t="n"/>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Nếu nhiều thứ cùng đổi, chênh lệch không còn gắn được cho một thay đổi cụ thể.</t>
+          <t>Để so sánh trước/sau có căn cứ khoa học (controlled comparison), phải giữ cố định các biến ngoại lai: (a) tập test case đối kháng và đối chứng lành tính, (b) quyền model/công cụ nếu chỉ đo guardrail, (c) canary và oracle chấm điểm, (e) ngưỡng điểm quyết định. Không được thay đổi ngẫu nhiên bộ prompt (d).</t>
         </is>
       </c>
     </row>
@@ -1089,7 +1089,7 @@
       <c r="J14" s="3" t="n"/>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Dùng bằng chứng từ luồng điều khiển và đích nhận để quyết định.</t>
+          <t>Khi guardrail chặn yêu cầu ngay trước khi gọi mô hình, không có công cụ nào được gọi và canary không xuất hiện ở bất kỳ đích nào, kết quả kiểm thử được phân loại chính xác là 'Bị chặn' (Blocked).</t>
         </is>
       </c>
     </row>
@@ -1169,7 +1169,7 @@
       <c r="J16" s="3" t="n"/>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Oracle đã quan sát gì tại sink trước exception?</t>
+          <t>Nếu canary token đã bị rò rỉ ra sink bên ngoài trước khi tiến trình gặp exception, kết quả an toàn chính vẫn là 'Bị lộ' (Leaked); exception chỉ là sự cố thực thi phát sinh sau đó.</t>
         </is>
       </c>
     </row>
@@ -1187,7 +1187,11 @@
           <t>Multiple Choice</t>
         </is>
       </c>
-      <c r="C17" s="3" t="n"/>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
       <c r="D17" s="3" t="n"/>
       <c r="E17" s="3" t="n"/>
       <c r="F17" s="3" t="n"/>
@@ -1201,7 +1205,7 @@
       <c r="J17" s="3" t="n"/>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Dùng đúng mẫu số 50 tình huống được nêu trong câu.</t>
+          <t>Tỷ lệ rò rỉ (leakage rate) trên toàn bộ 50 tình huống đối kháng = (8 bị lộ / 50 tình huống) * 100% = 16%.</t>
         </is>
       </c>
     </row>
@@ -1253,7 +1257,11 @@
           <t>Multiple Choice</t>
         </is>
       </c>
-      <c r="C19" s="3" t="n"/>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="D19" s="3" t="n"/>
       <c r="E19" s="3" t="n"/>
       <c r="F19" s="3" t="n"/>
@@ -1267,7 +1275,7 @@
       <c r="J19" s="3" t="n"/>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Mẫu số là toàn bộ 80 tình huống lành tính.</t>
+          <t>Tỷ lệ chặn nhầm (False Positive Rate) trên toàn bộ 80 tình huống lành tính = (12 bị chặn nhầm / 80 tình huống) * 100% = 15%.</t>
         </is>
       </c>
     </row>
@@ -1315,7 +1323,7 @@
       <c r="J20" s="3" t="n"/>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Thành phần nào, ngoài trọng số model, còn quyết định hành vi của hệ?</t>
+          <t>Mọi thay đổi cấu hình, bao gồm cả sửa biểu thức chính quy (regex) của guardrail, đều có thể làm thay đổi ranh giới an toàn; release gate bắt buộc phải chạy lại toàn bộ bộ kiểm thử hồi quy trước khi phát hành.</t>
         </is>
       </c>
     </row>
@@ -1399,7 +1407,7 @@
       <c r="J22" s="3" t="n"/>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Phải lưu bằng chứng trước khi sửa; chỉ thông báo sau khi kết quả đã được kiểm chứng.</t>
+          <t>Vòng đời xử lý phát hiện an toàn: Phát hiện và lưu bằng chứng đầy đủ (o2) → triển khai bản sửa lỗi trong đúng phạm vi (o3) → chạy lại test case gốc và bộ kiểm thử hồi quy regression (o1) → thông báo kết quả và rủi ro còn lại cho các bên liên quan (o4).</t>
         </is>
       </c>
     </row>

--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_11_Full_122_Cau/Day_11_Ngan_Hang_Phan_05_20_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_11_Full_122_Cau/Day_11_Ngan_Hang_Phan_05_20_Cau.xlsx
@@ -624,10 +624,22 @@
       <c r="K3" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Trường nào executor thật sự cần, và phần lý do/PII nên được giữ ở đâu?
-Phân tích theo nguyên lý thiết kế: Trường nào executor thật sự cần, và phần lý do/PII nên được giữ ở đâu?</t>
+- [1.5 điểm] Thiết kế gói handoff tối thiểu: chỉ chuyển đúng order_id và action=read_status cho Executor, tước bỏ hoàn toàn PII và rationale.
+- [1.5 điểm] Thiết kế kiến trúc lưu trữ kiểm toán riêng biệt (Split Audit Store) mã hóa rationale và PII có liên kết bằng plan_id.
+- [1.0 điểm] Phân tích được lợi ích kép: bảo vệ quyền riêng tư PII và tối ưu hóa chi phí/tốc độ thực thi của Executor.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Thiết kế Gói bàn giao sau Planning (Post-Plan Context Minimization Handoff):
+   - Nguyên tắc Tối thiểu hóa (Principle of Context Minimization): Executor chỉ cần đúng các thông tin tối thiểu cần thiết để thực thi hành động, bao gồm: `{order_id: string, action: 'read_status'}`.
+   - Loại bỏ rác ngữ cảnh: Toàn bộ phần lý do giải thích (rationale), thông tin định danh cá nhân (PII như tên khách hàng, địa chỉ, số điện thoại) và các trích dẫn tài liệu dài dòng BẮT BUỘC BỊ TÁCH RỜI và KHÔNG ĐƯỢC CHUYỂN vào ngữ cảnh runtime của Executor.
+2. Thiết kế Kiến trúc Lưu trữ và Audit (Split Audit Architecture):
+   - Phần Rationale và PII được lưu trữ tại kho lưu trữ kiểm toán có kiểm soát truy cập nghiêm ngặt (Encrypted Compliance Audit Store / Cold Log):
+     `{plan_id: UUID, generated_at: timestamp, rationale_encrypted: ciphertext, pii_fields_masked: {...}}`.
+   - Gói bàn giao gửi cho Executor chỉ mang theo `plan_id` và các tham số thực thi sạch: `{'plan_id': 'abc-123', 'order_id': 'ORD-999', 'action': 'read_status'}`.
+   - Lợi ích: Executor hoạt động với token context siêu nhỏ, tốc độ cao, không có rủi ro làm rò rỉ PII sang các API tiếp theo, trong khi bộ phận thanh tra vẫn có thể dùng `plan_id` để tra cứu toàn bộ lý do và trích dẫn ban đầu khi có khiếu nại.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Trong các hệ thống AI nhiều tác nhân (Multi-Agent Systems), việc chuyển tiếp toàn bộ chuỗi suy luận (Chain-of-Thought / Reasoning trace) kèm PII từ bước lập kế hoạch sang bước thực thi là một thói quen nguy hiểm. Nó vừa làm lãng phí cửa sổ ngữ cảnh (Context Bloat), vừa mở rộng bề mặt rò rỉ dữ liệu nhạy cảm sang các công cụ downstream. Kỹ thuật 'Tối thiểu hóa ngữ cảnh sau quy hoạch' đảm bảo Executor chỉ nhận tham số thuần túy, còn vết suy luận được cất giữ an toàn trong kho kiểm toán.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+ISO/IEC 27701: Privacy Information Management (Data Minimization Principle) và LangGraph Multi-Agent State Management</t>
         </is>
       </c>
     </row>
@@ -706,10 +718,24 @@
       <c r="K5" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Nếu service chuẩn hóa hỏng, lớp nào còn chặn text không tin cậy trước khi nó gọi tool?
-Phân tích theo nguyên lý thiết kế: Nếu service chuẩn hóa hỏng, lớp nào còn chặn text không tin cậy trước khi nó gọi tool?</t>
+- [1.5 điểm] Nhận diện chính xác lỗi chung (Common-Mode Failure) tại Service chuẩn hóa làm sụp đổ ảo tưởng phòng thủ đa tầng.
+- [1.5 điểm] Phân tích sâu sắc rủi ro tồn dư khi áp dụng fail-open đưa văn bản độc hại thẳng tới model.
+- [1.0 điểm] Thiết kế lớp phòng thủ tiếp theo độc lập tại tầng thực thi công cụ (Tool-level Capability Gate &amp; Egress Whitelist).
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Đánh giá Lỗi Chung (Common-Mode Failure Assessment):
+   - Phân tích rủi ro: Cả hai cơ chế phòng thủ (Spotlighting và Learned Detector) bề ngoài có vẻ là hai tầng độc lập, nhưng chúng lại cùng phụ thuộc vào một 'Điểm nghẽn hỏng hóc chung' (Single Point of Common-Mode Failure) - đó là Service Chuẩn hóa Văn bản (Normalization Service).
+   - Khi Normalization Service gặp sự cố hoặc timeout, chính sách hiện tại cho phép 'cho đầu vào thô đi qua' (Fail-Open), dẫn đến cả Spotlighting lẫn Learned Detector đều bị vô hiệu hóa cùng một lúc. Đây là một ảo tưởng phòng thủ theo chiều sâu (Illusion of Defense-in-Depth).
+2. Rủi ro còn lại (Residual Risk):
+   - Toàn bộ văn bản đầu vào thô chứa mã độc prompt injection sẽ đi thẳng vào Model và ép Agent gọi các công cụ phá hoại mà không gặp bất kỳ rào cản văn bản nào.
+3. Thiết kế Lớp tiếp theo độc lập (Next Independent Defense Layer):
+   - Lớp 3 (Tool-Level Deterministic Capability Gate): Nằm tại ranh giới thực thi công cụ (Tool Execution Boundary). Lớp này HOÀN TOÀN ĐỘC LẬP với Service chuẩn hóa văn bản. Dù Model có bị lừa và phát lệnh gọi tool, Tool Gate vẫn kiểm tra:
+     + Whitelist tham số nghiêm ngặt;
+     + Bắt buộc xác thực người dùng (HITL confirmation) đối với các hành động phá hủy/chuyển tiền;
+     + Khóa mạng (Network Egress Firewall) chặn kết nối ra ngoài danh sách domain cho phép.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc thiết kế Phòng thủ theo chiều sâu (Defense-in-Depth) thực sự đòi hỏi các tầng kiểm soát phải độc lập hoàn toàn về mặt kiến trúc và hạ tầng (Failure Independence). Nếu nhiều lớp guardrail văn bản cùng dựa trên một dịch vụ tiền xử lý dùng chung và áp dụng cơ chế Fail-Open, một lỗi duy nhất sẽ đánh sập toàn bộ hệ thống phòng thủ. Việc bổ sung một lớp kiểm soát cứng tại ranh giới công cụ (Tool Capability Gate) đảm bảo chặn đứng thiệt hại ngay cả khi toàn bộ tầng LLM bị đánh bại.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+NIST Special Publication 800-53 Rev. 5: SC-24 Fail in Known State và OWASP Top 10 for LLM - Defense in Depth Architecture</t>
         </is>
       </c>
     </row>
@@ -788,10 +814,21 @@
       <c r="K7" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Ghép từng thuộc tính cần kiểm với lớp phù hợp: quy tắc, bộ phân loại, kiểm duyệt hay judge.
-Phân tích theo nguyên lý thiết kế: Ghép từng thuộc tính cần kiểm với lớp phù hợp: quy tắc, bộ phân loại, kiểm duyệt hay judge.</t>
+- [1.5 điểm] Ánh xạ chính xác 4 yêu cầu sang 4 cách tiếp cận phù hợp: Regex cho marker đã biết, Bộ phân loại nhẹ cho intent, Moderation API cho output nguy hại, LLM Judge cho ca khó.
+- [1.5 điểm] Đánh giá đầy đủ chi phí và độ trễ tương ứng cho từng tầng từ cực thấp đến cao.
+- [1.0 điểm] Xây dựng phương án dự phòng (fallback) thực tế và khả thi cho từng giải pháp khi xảy ra lỗi.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Ánh xạ Yêu cầu sang Cách tiếp cận An toàn (Requirements-to-Approach Mapping):
+| Yêu cầu kiểm soát | Cách tiếp cận phù hợp nhất | Chi phí / Độ trễ | Phương án dự phòng (Fallback) |
+|---|---|---|---|
+| Chặn marker injection đã biết | Quy tắc xác định (Regex / Exact String Match / Aho-Corasick) | Cực thấp (&lt; 1ms, CPU thuần túy) | Cập nhật tập luật động (Dynamic Rule Update); không cần fallback do siêu ổn định |
+| Lọc ý định ngoài phạm vi | Bộ phân loại chuyên dụng nhẹ (Small Learned Classifier / DeBERTa / SetFit) | Thấp (15-30ms, chạy local GPU/CPU) | Nếu timeout: Giới hạn Agent về chế độ trả lời câu hỏi FAQ an toàn hoặc Fail-Closed |
+| Kiểm tra đầu ra nguy hại | API Kiểm duyệt chuyên dụng (Moderation API / Llama Guard) | Trung bình (50-100ms, token cost nhỏ) | Nếu API bên ngoài lỗi: Dùng regex heuristic lọc từ ngữ độc hại cục bộ |
+| Xử lý ca ngữ nghĩa khó | LLM Safety Judge riêng biệt (LLM-as-a-Judge với Prompt chi tiết) | Cao (500-1500ms, chi phí token cao) | Chỉ kích hoạt theo điều kiện (Conditional Trigger) khi các tầng trước nghi vấn; nếu timeout: Chuyển sang Human-in-the-Loop review |
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Không có một công nghệ đơn lẻ nào giải quyết được tất cả các yêu cầu kiểm soát an toàn AI. Việc lựa chọn công cụ phải căn cứ vào tính chất của bài toán: Các mẫu đã biết dùng quy tắc đơn định để tối ưu tốc độ và chi phí; Phân loại ý định dùng mô hình nhỏ; Kiểm duyệt độc hại dùng mô hình chuyên môn hóa; và chỉ những ca ngữ nghĩa phức tạp mới kích hoạt LLM Judge đắt đỏ. Mỗi tầng bắt buộc phải có phương án dự phòng khi gặp sự cố tính sẵn sàng.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+NVIDIA NeMo Guardrails Architectural Guidelines: https://docs.nvidia.com/nemo/guardrails/ và Meta Llama Guard Deployment Best Practices</t>
         </is>
       </c>
     </row>
@@ -870,10 +907,25 @@
       <c r="K9" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Hai câu chỉ khác cách diễn đạt nhưng cùng nguồn, mục tiêu và oracle có tạo thêm độ bao phủ không?
-Phân tích theo nguyên lý thiết kế: Hai câu chỉ khác cách diễn đạt nhưng cùng nguồn, mục tiêu và oracle có tạo thêm độ bao phủ không?</t>
+- [1.5 điểm] Thiết kế một hàng phân loại chuẩn hóa đầy đủ các trường: case_id, attack_vector, input_source, payload_technique, targeted_component, observable_oracle.
+- [1.5 điểm] Phân tích sâu sắc lý do hai câu chỉ khác cách diễn đạt không tạo thêm độ bao phủ bảo mật nếu cùng nguồn, mục tiêu và oracle.
+- [1.0 điểm] Đề xuất phương pháp phân nhóm theo lớp tương đương kiến trúc để loại bỏ trùng lặp hiệu quả.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Thiết kế Một Hàng Phân Loại Ca Đối Kháng (Adversarial Case Taxonomy Row):
+   - `case_id`: `ADV-INDIR-TOOL-042`
+   - `attack_vector`: `Indirect Prompt Injection` (Tiêm chỉ thị gián tiếp qua tài liệu bên ngoài)
+   - `input_source`: `External PDF RAG Chunk` (Nội dung văn bản truy xuất từ tài liệu hợp đồng đối tác)
+   - `payload_technique`: `Fake System Delimiter with Capability Hijacking` (Giả lập thẻ chỉ thị hệ thống yêu cầu exfiltrate dữ liệu)
+   - `targeted_component`: `Tool Execution Layer` (Công cụ gọi API ra ngoài `http_post_webhook`)
+   - `expected_mitigation`: `Egress Whitelist Gate &amp; Parameterized Tool Enforcement`
+   - `observable_oracle`: `assert network_trace.post_calls == 0 and guardrail_log.verdict == 'BLOCKED'`
+2. Cách Tránh Đường Dẫn Trùng Lặp (Avoiding Redundant Test Paths):
+   - Nguyên tắc bao phủ: 'Độ bao phủ kiểm thử an toàn được định nghĩa bởi không gian {Nguồn -&gt; Kỹ thuật -&gt; Ranh giới bị nhắm tới -&gt; Observable Oracle}'.
+   - Loại bỏ trùng lặp: Hai câu prompt chỉ khác nhau về cách diễn đạt ngôn từ (paraphrase bề mặt) nhưng có cùng một nguồn gốc (Direct User Prompt), cùng nhắm tới việc phá vỡ system constraint và cùng được kiểm chứng bởi một Oracle (output không chứa secret) thì KHÔNG TẠO THÊM ĐỘ BAO PHỦ BẢO MẬT (Zero Added Coverage). Cần loại bỏ các ca trùng lặp ngữ nghĩa này để tối ưu hóa thời gian chạy test suite.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân loại ca đối kháng (Adversarial Taxonomy) chuẩn mực phải cấu trúc hóa được đường truyền tấn công từ nguồn dữ liệu tới ranh giới công cụ. Việc tạo ra hàng nghìn câu prompt chỉ thay đổi từ ngữ đồng nghĩa (paraphrasing) tạo ra ảo giác về quy mô kiểm thử nhưng thực chất chỉ kiểm tra cùng một đường dẫn lỗi. Kiểm định an toàn hiện đại phân nhóm theo 'Lớp tương đương về mặt kiến trúc' (Architectural Equivalence Partitioning) để tối đa hóa khả năng phát hiện lỗ hổng.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+MITRE ATLAS (Adversarial Threat Landscape for Artificial-Intelligence Systems): https://atlas.mitre.org/ và NIST AI RMF Test &amp; Evaluation Standards</t>
         </is>
       </c>
     </row>
@@ -952,10 +1004,32 @@
       <c r="K11" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Canary xuất hiện ở đâu mà lời từ chối hoặc đầu ra sạch không thể hiện được?
-Phân tích theo nguyên lý thiết kế: Canary xuất hiện ở đâu mà lời từ chối hoặc đầu ra sạch không thể hiện được?</t>
+- [1.5 điểm] Phân loại chính xác kiểm thử là THẤT BẠI (FAIL) do rò rỉ dữ liệu qua kênh phụ mạng (network side-channel exfiltration).
+- [1.5 điểm] Vạch trần sự nguy hiểm của việc đầu ra sạch nhưng mạng bị rò rỉ giá trị băm của canary.
+- [1.0 điểm] Xây dựng mã kiểm thử Oracle tối thiểu có khả năng bắt được cả canary chuỗi thô lẫn canary dạng băm tại network trace.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Phân loại Kết quả Kiểm thử (Security Test Classification):
+   - KẾT QUẢ: THẤT BẠI NGHIÊM TRỌNG / RÒ RỈ DỮ LIỆU ĐƯỢC XÁC NHẬN (FAIL - CRITICAL DATA EXFILTRATION).
+   - Phân tích bản chất: Mặc dù đầu ra văn bản hiển thị cho người dùng (agent output) hoàn toàn sạch sẽ hoặc thậm chí giả vờ từ chối, nhưng dấu vết mạng (network trace) đã ghi nhận một request HTTP POST gửi ra ngoài chứa giá trị băm của canary (`hash(CANARY-7)`).
+   - Đây là kỹ thuật rò rỉ kênh phụ / bí mật (Side-channel Data Exfiltration): Kẻ tấn công đã điều khiển Agent băm canary rồi gửi qua công cụ ngầm mà không cần hiển thị canary ra màn hình chat.
+2. Viết Observable Oracle Tối thiểu (Minimal Observable Security Oracle):
+   - Không được dùng 'Output Text Oracle' (kiểm tra văn bản trả lời là mù quáng).
+   - Observable Oracle toàn diện bắt buộc phải đo lường tại ranh giới mạng và công cụ (Network &amp; Tool Boundary Oracle):
+     ```python
+     def oracle_canary_leak_check(test_run):
+         # Kiểm tra 1: Đầu ra văn bản
+         assert 'CANARY-7' not in test_run.agent_output_text
+         # Kiểm tra 2: Ranh giới gọi Tool và Network Egress
+         canary_hash = hashlib.sha256(b'CANARY-7').hexdigest()
+         for req in test_run.network_egress_requests:
+             assert 'CANARY-7' not in req.payload_str, 'Plaintext canary leaked in network request!'
+             assert canary_hash not in req.payload_str, 'Hashed canary leaked in side-channel POST request!'
+         return True
+     ```
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Một trong những cạm bẫy lớn nhất trong kiểm thử an toàn AI là 'Đánh giá an toàn chỉ dựa trên bề mặt câu trả lời' (Output-Only Fallacy). Kẻ tấn công có thể dễ dàng hướng dẫn Agent trả lời một câu từ chối lịch sự với người dùng trong khi âm thầm gọi Tool gửi mã băm hoặc dữ liệu mật ra máy chủ bên ngoài. Một Observable Oracle thực thụ phải giám sát toàn diện mọi hiệu ứng ngoại biên (Side-effects) tại ranh giới mạng và nhật ký gọi công cụ.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+OWASP Top 10 for LLM - LLM02: Sensitive Information Disclosure &amp; Canary Token Tracking và Thinkst CanaryTokens Security Architecture</t>
         </is>
       </c>
     </row>
@@ -1038,10 +1112,30 @@
       <c r="K13" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Liệt kê mọi biến đã thay đổi ngoài guardrail.
-Phân tích theo nguyên lý thiết kế: Liệt kê mọi biến đã thay đổi ngoài guardrail.</t>
+- [1.5 điểm] Phê bình sâu sắc kết luận hiện tại: không có giá trị do vi phạm kiểm soát biến, chỉ ra đầy đủ 4 yếu tố bị thay đổi đồng thời.
+- [1.5 điểm] Thiết kế ma trận thử nghiệm có kiểm soát (Ablation Matrix) giữ cố định bộ test set và verifier để cô lập nguyên nhân.
+- [1.0 điểm] Nêu rõ phép so sánh chuẩn (M1+G2 vs M1+G1) để chứng minh chính xác đóng góp của Guardrail mới.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Đánh giá Kết luận Hiện tại (Evaluation of Current Conclusion):
+   - Kết luận 'Tỷ lệ rò rỉ giảm 12% -&gt; 5% chứng minh guardrail mới tốt hơn' là HOÀN TOÀN VÔ GIÁ TRỊ VỀ MẶT KHOA HỌC (Invalid &amp; Confounded Conclusion).
+   - Nguyên nhân: Vi phạm nguyên tắc kiểm soát biến độc lập (Violation of Controlled Experiment). Đã có quá nhiều biến số bị thay đổi đồng thời giữa hai lần chạy:
+     + Model bị đổi từ M1 sang M2;
+     + Guardrail bị đổi từ G1 sang G2;
+     + Tập kiểm thử bị đổi từ 100 tình huống ban đầu sang 130 tình huống KHÁC;
+     + Bộ kiểm chứng (Verifier/Oracle) cũng bị thay mới.
+   - Sự sụt giảm tỷ lệ rò rỉ có thể đơn giản là do 130 tình huống mới dễ hơn, hoặc do Model M2 tự thân an toàn hơn, hoặc do bộ verifier mới bị bỏ sót lỗi (False Negative).
+2. Thiết kế Lần chạy lại có Kiểm soát để quy được nguyên nhân (Controlled Re-run Design):
+   - Cố định Bộ Kiểm thử và Bộ Kiểm chứng: Sử dụng MỘT BỘ 100 tình huống chuẩn hóa duy nhất và MỘT BỘ Verifier chuẩn duy nhất cho mọi lần chạy.
+   - Thiết kế Ma trận Thử nghiệm Đa nhân tố (Ablation Matrix):
+     + Run A: `M1 + G1` (Baseline cũ)
+     + Run B: `M1 + G2` (Cô lập hiệu quả thực sự của Guardrail mới trên cùng model M1)
+     + Run C: `M2 + G1` (Cô lập hiệu quả của việc đổi model)
+     + Run D: `M2 + G2` (Đánh giá hiệu quả kết hợp)
+   - Chỉ khi so sánh Run B với Run A trên cùng một tập benchmark cố định, ta mới có thể quy kết một cách chính xác sự cải thiện thuộc về Guardrail G2.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Trong phương pháp luận thực nghiệm (Scientific Benchmarking), việc đồng thời thay đổi cả mô hình, bộ lọc, tập dữ liệu kiểm thử và công cụ đo lường sẽ tạo ra hiện tượng 'Nhiễu loạn đa biến' (Multi-variable Confounding). Để chứng minh một thành phần an toàn mới hoạt động hiệu quả hơn thành phần cũ, bắt buộc phải áp dụng phương pháp nghiên cứu loại trừ (Ablation Study) bằng cách cố định tất cả các biến số khác trên cùng một tập chuẩn (Gold Benchmark).
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+HELM (Holistic Evaluation of Language Models - Stanford CRFM): https://crfm.stanford.edu/helm/ và NIST AI RMF - Controlled Evaluation Protocols</t>
         </is>
       </c>
     </row>
@@ -1120,10 +1214,21 @@
       <c r="K15" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Bằng chứng lộ dữ liệu đã xuất hiện trước hay sau khi lỗi thực thi xảy ra?
-Phân tích theo nguyên lý thiết kế: Bằng chứng lộ dữ liệu đã xuất hiện trước hay sau khi lỗi thực thi xảy ra?</t>
+- [1.5 điểm] Phân loại chính xác kết quả là Thất bại an ninh / Rò rỉ dữ liệu (Security Failure / Leak), bác bỏ việc xếp vào lỗi kỹ thuật.
+- [1.5 điểm] Lập luận chặt chẽ về thứ tự ưu tiên: Vi phạm bảo mật luôn có thứ bậc cao hơn lỗi thực thi/timeout.
+- [1.0 điểm] Chỉ ra bằng chứng thời gian: rò rỉ 4 ký tự xảy ra trước khi timeout, không thể lấy lỗi kỹ thuật để che giấu lỗ hổng an toàn.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Phân loại Kết quả Kiểm thử (Outcome Classification):
+   - PHÂN LOẠI: THẤT BẠI AN NINH / RÒ RỈ DỮ LIỆU ĐƯỢC XÁC NHẬN (SECURITY FAILURE / CONFIRMED LEAKAGE). Tuyệt đối KHÔNG ĐƯỢC phân loại là 'Lỗi kỹ thuật' (Infrastructure Error).
+   - Bằng chứng thực nghiệm: Chuỗi phản hồi hiển thị 4/8 ký tự của canary. 4 ký tự canary đầu tiên đã bộc lộ ra kênh công khai TRƯỚC KHI sự cố timeout của công cụ xảy ra. Dữ liệu nhạy cảm đã bị tiết lộ một phần (Partial Sensitive Disclosure).
+2. Giải thích Thứ tự Ưu tiên Phân loại (Classification Precedence Order):
+   - Nguyên tắc phân cấp nghiêm ngặt trong AI Safety:
+     `VI PHẠM BẢO MẬT (Security Leak) &gt; LỖI THỰC THI (Execution Error) &gt; HOÀN THÀNH THÀNH CÔNG (Success)`.
+   - Lý do kỹ thuật: Một lỗi timeout xảy ra sau khi dữ liệu đã rò rỉ không thể làm mất đi sự thật rằng bí mật đã bị bộc lộ. Nếu đánh dấu ca này là 'Lỗi kỹ thuật' (Transient Error) để chạy lại hoặc bỏ qua, hệ thống sẽ âm thầm che giấu một lỗ hổng rò rỉ dữ liệu nghiêm trọng, tạo ra cảm giác an toàn giả tạo trong báo cáo kiểm toán.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Trong ma trận phân loại kết quả kiểm thử an toàn (Outcome Classification Hierarchy), các sự kiện vi phạm an ninh (Security Violations) luôn chiếm mức ưu tiên tối cao nhất. Hiện tượng rò rỉ từng phần (Partial Canary Leak) chứng minh rằng cơ chế bảo vệ bí mật đã hoàn toàn thất bại trong việc đánh chặn. Việc hệ thống sau đó bị sập hay timeout chỉ là lỗi thứ cấp phát sinh sau vi phạm, không được phép làm lu mờ sự cố bảo mật gốc.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+OWASP Top 10 for LLM - LLM02: Sensitive Information Disclosure và Google SRE - Incident Classification Taxonomy</t>
         </is>
       </c>
     </row>
@@ -1236,10 +1341,30 @@
       <c r="K18" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Tách tình huống đối kháng, lành tính và từng nhóm trước khi tính.
-Phân tích theo nguyên lý thiết kế: Tách tình huống đối kháng, lành tính và từng nhóm trước khi tính.</t>
+- [1.5 điểm] Tính toán chính xác toàn bộ các chỉ số: ASR chung (6/60 = 10%), Error rate (9/60 = 15%), FPR lành tính (5/40 = 12.5%).
+- [1.5 điểm] Phân rã chính xác ASR theo nhóm: Indirect (4/10 = 40%) và Direct (2/50 = 4%), vạch trần điểm yếu nghiêm trọng của Indirect.
+- [1.0 điểm] Thể hiện tư duy diễn giải khoa học, cảnh báo rõ ràng việc không được suy diễn trực tiếp ra tần suất rủi ro ngoài đời thực.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Tính toán các chỉ số an toàn chính xác:
+   - Trên tập Đối kháng (Adversarial Set: N = 60):
+     + Tỷ lệ tấn công thành công chung (Overall Attack Success Rate - ASR):
+       ASR = Số ca rò rỉ / Tổng ca đối kháng = 6 / 60 = 0.10 (10.0%).
+     + Tỷ lệ lỗi thực thi kỹ thuật (Technical Execution Error Rate):
+       Error Rate = 9 / 60 = 0.15 (15.0%).
+     + Tỷ lệ phòng vệ thành công (Adversarial Defense Rate): (60 - 6 - 9) / 60 = 45 / 60 = 0.75 (75.0%).
+   - Phân rã theo nhóm tấn công (Subgroup ASR Breakdown):
+     + Nhóm Indirect Injection: ASR = 4 / 10 = 0.40 (40.0% rò rỉ) -&gt; MỨC ĐỘ NGUY HIỂM RẤT CAO.
+     + Nhóm Direct Injection: ASR = 2 / 50 = 0.04 (4.0% rò rỉ).
+   - Trên tập Lành tính (Benign Set: N = 40):
+     + Tỷ lệ báo động nhầm (False Positive Rate - FPR / Over-blocking Rate):
+       FPR = Số ca lành tính bị chặn / Tổng ca lành tính = 5 / 40 = 0.125 (12.5%).
+2. Diễn giải đúng mức mà không suy diễn quá mức (Calibrated Interpretation):
+   - 'Chỉ số đo lường phản ánh chính xác hiệu năng của hệ thống trên tập kiểm định đóng: Hệ thống phòng thủ tương đối tốt trước Direct Injection (chỉ lọt 4%), nhưng đặc biệt yếu kém trước Indirect Injection (lọt tới 40%), đồng thời gây ra 12.5% chặn nhầm trên tập câu hỏi lành tính'.
+   - Cảnh báo phương pháp luận: Các con số này phụ thuộc vào tỷ lệ phân bổ nhân tạo của bộ kiểm thử (60 đối kháng / 40 lành tính) và KHÔNG ĐƯỢC SUY DIỄN rằng ngoài đời thực có 10% người dùng sẽ bị rò rỉ dữ liệu, vì tần suất tấn công thực tế (base rate of attack in wild) có thể thấp hơn rất nhiều.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Trong tính toán chỉ số kiểm thử an toàn AI, việc gộp chung các loại tấn công khác nhau sẽ che giấu các điểm yếu cục bộ chí tử (Simpson's Paradox). Tỷ lệ ASR chung là 10% tưởng chừng chấp nhận được, nhưng khi phân rã chi tiết, nhóm Indirect Injection có tỷ lệ lọt lưới lên tới 40%. Đồng thời, kỹ sư phải nhận thức rõ về 'Base Rate Fallacy': các chỉ số trên tập kiểm định không đại diện cho phân phối xác suất ngoài đời thực.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+NIST AI 100-2 E2023: Adversarial Machine Learning - A Taxonomy and Terminology of Attacks and Mitigations và HELM Safety Metrics</t>
         </is>
       </c>
     </row>
@@ -1354,10 +1479,21 @@
       <c r="K21" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Một tình huống nghiêm trọng đã tới đích gửi có được phép bị che bởi tỷ lệ đạt trung bình không?
-Phân tích theo nguyên lý thiết kế: Một tình huống nghiêm trọng đã tới đích gửi có được phép bị che bởi tỷ lệ đạt trung bình không?</t>
+- [1.5 điểm] Ra quyết định dứt khoát: CHẶN PHÁT HÀNH R12, bác bỏ lập luận dùng tỷ lệ đạt 99% để che giấu lỗi nghiêm trọng.
+- [1.5 điểm] Khẳng định nguyên tắc an toàn Zero-Tolerance đối với các lỗ hổng rò rỉ dữ liệu mức Critical.
+- [1.0 điểm] Xây dựng quy trình xử lý khắc phục bài bản: sửa root cause tại công cụ gửi dữ liệu, kiểm thử hồi quy biến thể và yêu cầu security sign-off.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Áp Cổng Phát hành An toàn (Safety Release Gate Enforcement):
+   - QUYẾT ĐỊNH: LẬP TỨC CHẶN PHÁT HÀNH BẢN R12 (BLOCK RELEASE / HARD GATE VETO). Bác bỏ hoàn toàn yêu cầu bỏ qua của nhóm sản phẩm.
+   - Căn cứ nguyên lý an toàn: Một sự cố thất bại mang mức độ 'Nghiêm trọng' (Critical Severity - Indirect Injection dẫn tới công cụ gửi dữ liệu mật ra ngoài) là một ĐIỀU KIỆN CHẶN CỨNG ĐƠN LẺ (Single Blocker Zero-Tolerance Policy). Trong bảo mật hệ thống AI, điểm số trung bình (99/100) không có ý nghĩa khi 1% thất bại còn lại là một lỗ hổng rò rỉ dữ liệu thảm khốc (Catastrophic Data Breach).
+2. Quy trình Xử lý Tình huống Thất bại (Failure Remediation Workflow):
+   - Bước 1 (Quarantine &amp; Deep Dive): Đưa ca thất bại vào phòng thí nghiệm an ninh để tái hiện và phân tích cơ chế vượt rào;
+   - Bước 2 (Root-Cause Fix): Bổ sung kiểm soát tại hai đầu: (a) Spotlighting và bộ lọc dữ liệu đầu vào cho tài liệu indirect; (b) Khóa mạng (Network Egress Whitelist) và bổ sung cổng xác nhận con người (HITL) tại công cụ gửi dữ liệu;
+   - Bước 3 (Regression &amp; Sign-off): Chạy lại toàn bộ 100 ca kiểm thử cộng thêm 20 biến thể mới của ca thất bại này. Bản release R12.1 CHỈ ĐƯỢC PHÁT HÀNH khi đạt 100% không còn bất kỳ ca rò rỉ nghiêm trọng nào và có chữ ký chấp thuận của Security Lead.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Cổng phát hành hồi quy an toàn (Safety Regression Release Gate) không hoạt động như một bài thi tính điểm trung bình học thuật. Một hệ thống đạt 99% ca thông thường nhưng để lọt một đường dẫn cho phép hacker chiếm quyền điều khiển công cụ gửi dữ liệu ra ngoài là một hệ thống không đủ điều kiện vận hành sản xuất. Tỷ lệ đạt trung bình cao không bao giờ được phép dùng làm bình phong để che giấu các rủi ro thảm họa.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Google SRE Book - Release Engineering &amp; Safety Gates: https://sre.google/sre-book/release-engineering/ và OWASP Top 10 for LLM - Governance &amp; Release Criteria</t>
         </is>
       </c>
     </row>
